--- a/Xlsx filer/Brugsen_produkter.xlsx
+++ b/Xlsx filer/Brugsen_produkter.xlsx
@@ -4069,41 +4069,41 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Irma Vitendo tomater</t>
+          <t>Xtra kyllingebryst eller -inderfilet</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Xtra</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>600 g</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>55,00. kr/kg</t>
+          <t>81,67. kr/kg</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1029918</t>
+          <t>1043648</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9214c0637e5db88b766d162f2be5cdba&amp;w=552&amp;s=99accb735acf04b56143b17b8901f70b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9751d328ddbe09d3da2523b802dbadbb%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa86d0b8b5fd11fb3113e1eeb242fbf6b&amp;w=552&amp;s=5dce06b9ff3c91d7141ade977cfa84e5</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>cec6396b9230b399</t>
+          <t>d8ed1dce5a28661a</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>1 bakke</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -4125,41 +4125,41 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bread &amp; Butter eller Terrunyo</t>
+          <t>Pågen brød</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bread</t>
+          <t>Pågen</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>650-900 g</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>132,00. kr/l</t>
+          <t>30,77. kr/kg</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1029954</t>
+          <t>1029925</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5dd89b35680a0c14456e21ee6fde279c&amp;w=265&amp;s=b0cba3fb9ecd1c20b9c174139682bd65</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2f34c919c36beb31fbd04735bc4d1849%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fffb4ac0a867e103689274ee2eea247c9&amp;w=552&amp;s=82768826187e4288f009c2660607580c</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>dc2763a71ec8278a</t>
+          <t>d9e0661c770b3e34</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -4181,41 +4181,41 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Dansk Kalv entrecote eller ribeye</t>
+          <t>Danske frilandsæg</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dansk</t>
+          <t>Danske</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>350 g</t>
+          <t>10 stk</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>282,86. kr/kg</t>
+          <t>2,60. kr/stk</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1029911</t>
+          <t>1029921</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8ffb5fbcc1ca0fe7443880ede1b148a3%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F502850b35cdec1e51ce717d700365acb&amp;w=252&amp;s=e6ece7abc7a477bdb0d4e862b3ab6a26</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbe29c136be04a69154119eb4a7a28207&amp;w=252&amp;s=ef3ffad95a21f7dd15fea1b3931bfd09</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>d07c07a2ccfc17c6</t>
+          <t>ca6a3595eb4ac4a5</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 bakke</t>
         </is>
       </c>
     </row>
@@ -4237,41 +4237,41 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sun Lolly</t>
+          <t>Coop Kylling</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>8 x 60 ml</t>
+          <t>750-1500 g</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>33,33. kr/l</t>
+          <t>50,67. kr/kg</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1029944</t>
+          <t>1029934</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2d2ca6d7211333213152f539af36de40%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0e2162e38a5aff5c21383b1b1f0471ec%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5ec9e01846238e9e7460635c83b53d68&amp;w=252&amp;s=6a28ba2f432a7178ab4d67c3bcb5c5a0</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F25f7d84484d16cb33ccea0ff03c6d5f0%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc1e84544869fd363dfae125fc838dccd%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8b289f68bfe8ed55c48973db006b5af9&amp;w=252&amp;s=6f8fd4efe81a6f7022809c64eb7c47ba</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>e2b117e6780f2559</t>
+          <t>9d15dcea925ac439</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -4293,41 +4293,41 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Valsemøllen kage-, brødblanding eller sukker</t>
+          <t>Pink Lady æbler</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Valsemøllen</t>
+          <t>Pink</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>400-2000 g</t>
+          <t>8 stk</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>42,50. kr/kg</t>
+          <t>2,75. kr/stk</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1029940</t>
+          <t>1043649</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F579b32a002ffa91cd94d35b2d784320d&amp;w=252&amp;s=a1d5f8f1eadd62b916f1e7d6ee52b8c6</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa58a25726c5bb867b1e32ab86c6316f6&amp;w=252&amp;s=2da8061ed049590b4d8db181aa96b57a</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>85c647f87c83236d</t>
+          <t>c1943e4b4c7aeb8c</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 bakke</t>
         </is>
       </c>
     </row>
@@ -4349,41 +4349,41 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Langelænder pølser</t>
+          <t>OTA solgryn</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Langelænder</t>
+          <t>OTA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>325-360 g</t>
+          <t>700 g</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>89,23. kr/kg</t>
+          <t>17,14. kr/kg</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1029924</t>
+          <t>1029939</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb4c4e33e0c7e682696281fe491faceb9%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F063e68ae8d1b5b4ca16fe29584c62c9c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa190d6311262bd3cc9bd7e2b5e27e703&amp;w=252&amp;s=9de01174b01e6973f9abde5fd96ae4d6</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F82d642042711f4691600acd343a21fa0&amp;w=252&amp;s=33514fd82fe1636c03ee57a341bd6e9e</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>83a55c58b1e7c639</t>
+          <t>c3c3b69a6c689699</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">

--- a/Xlsx filer/Brugsen_produkter.xlsx
+++ b/Xlsx filer/Brugsen_produkter.xlsx
@@ -1853,7 +1853,11 @@
           <t>Dagmartærte</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>30,00. kr/stk</t>

--- a/Xlsx filer/Brugsen_produkter.xlsx
+++ b/Xlsx filer/Brugsen_produkter.xlsx
@@ -4073,41 +4073,41 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Xtra kyllingebryst eller -inderfilet</t>
+          <t>Irma Vitendo tomater</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Xtra</t>
+          <t>Irma</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>600 g</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>81,67. kr/kg</t>
+          <t>55,00. kr/kg</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1043648</t>
+          <t>1029918</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9751d328ddbe09d3da2523b802dbadbb%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa86d0b8b5fd11fb3113e1eeb242fbf6b&amp;w=552&amp;s=5dce06b9ff3c91d7141ade977cfa84e5</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9214c0637e5db88b766d162f2be5cdba&amp;w=552&amp;s=99accb735acf04b56143b17b8901f70b</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>d8ed1dce5a28661a</t>
+          <t>cec6396b9230b399</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 bakke</t>
         </is>
       </c>
     </row>
@@ -4129,41 +4129,41 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pågen brød</t>
+          <t>Bread &amp; Butter eller Terrunyo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pågen</t>
+          <t>Bread</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>650-900 g</t>
+          <t>75 cl</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>30,77. kr/kg</t>
+          <t>132,00. kr/l</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1029925</t>
+          <t>1029954</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2f34c919c36beb31fbd04735bc4d1849%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fffb4ac0a867e103689274ee2eea247c9&amp;w=552&amp;s=82768826187e4288f009c2660607580c</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5dd89b35680a0c14456e21ee6fde279c&amp;w=265&amp;s=b0cba3fb9ecd1c20b9c174139682bd65</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>d9e0661c770b3e34</t>
+          <t>dc2763a71ec8278a</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -4185,41 +4185,41 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Danske frilandsæg</t>
+          <t>Dansk Kalv entrecote eller ribeye</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Danske</t>
+          <t>Dansk</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>10 stk</t>
+          <t>350 g</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2,60. kr/stk</t>
+          <t>282,86. kr/kg</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1029921</t>
+          <t>1029911</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbe29c136be04a69154119eb4a7a28207&amp;w=252&amp;s=ef3ffad95a21f7dd15fea1b3931bfd09</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8ffb5fbcc1ca0fe7443880ede1b148a3%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F502850b35cdec1e51ce717d700365acb&amp;w=252&amp;s=e6ece7abc7a477bdb0d4e862b3ab6a26</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>ca6a3595eb4ac4a5</t>
+          <t>d07c07a2ccfc17c6</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>1 bakke</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -4241,41 +4241,41 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Coop Kylling</t>
+          <t>Sun Lolly</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>750-1500 g</t>
+          <t>8 x 60 ml</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>50,67. kr/kg</t>
+          <t>33,33. kr/l</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1029934</t>
+          <t>1029944</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F25f7d84484d16cb33ccea0ff03c6d5f0%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc1e84544869fd363dfae125fc838dccd%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8b289f68bfe8ed55c48973db006b5af9&amp;w=252&amp;s=6f8fd4efe81a6f7022809c64eb7c47ba</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2d2ca6d7211333213152f539af36de40%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0e2162e38a5aff5c21383b1b1f0471ec%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5ec9e01846238e9e7460635c83b53d68&amp;w=252&amp;s=6a28ba2f432a7178ab4d67c3bcb5c5a0</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>9d15dcea925ac439</t>
+          <t>e2b117e6780f2559</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -4297,41 +4297,41 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pink Lady æbler</t>
+          <t>Valsemøllen kage-, brødblanding eller sukker</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pink</t>
+          <t>Valsemøllen</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>8 stk</t>
+          <t>400-2000 g</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2,75. kr/stk</t>
+          <t>42,50. kr/kg</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1043649</t>
+          <t>1029940</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa58a25726c5bb867b1e32ab86c6316f6&amp;w=252&amp;s=2da8061ed049590b4d8db181aa96b57a</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F579b32a002ffa91cd94d35b2d784320d&amp;w=252&amp;s=a1d5f8f1eadd62b916f1e7d6ee52b8c6</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>c1943e4b4c7aeb8c</t>
+          <t>85c647f87c83236d</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>1 bakke</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -4353,41 +4353,41 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>OTA solgryn</t>
+          <t>Langelænder pølser</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OTA</t>
+          <t>Langelænder</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>700 g</t>
+          <t>325-360 g</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>17,14. kr/kg</t>
+          <t>89,23. kr/kg</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1029939</t>
+          <t>1029924</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F82d642042711f4691600acd343a21fa0&amp;w=252&amp;s=33514fd82fe1636c03ee57a341bd6e9e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb4c4e33e0c7e682696281fe491faceb9%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F063e68ae8d1b5b4ca16fe29584c62c9c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa190d6311262bd3cc9bd7e2b5e27e703&amp;w=252&amp;s=9de01174b01e6973f9abde5fd96ae4d6</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>c3c3b69a6c689699</t>
+          <t>83a55c58b1e7c639</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">

--- a/Xlsx filer/Brugsen_produkter.xlsx
+++ b/Xlsx filer/Brugsen_produkter.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -619,41 +619,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Adobe eller Jam Shed</t>
+          <t>Santa Maria Tex Mex</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Santa</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>28-371 g</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>46,67. kr/l</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>35</v>
-      </c>
+          <t>356,43. kr/kg</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1029906</t>
+          <t>1029963</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe4833b1373365b6ffcd49ee76f87d35f&amp;w=252&amp;s=0c43a6b1c6e8d3f916660cf24d1c0797</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F861403ff8278bc91605620bb5efbd9a3&amp;w=552&amp;s=d7a80a2643a317b9b8c74e45a97f2fa6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>856a4aa55a6e1abd</t>
+          <t>e1ce6e721dc92236</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -661,11 +659,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1 flaske</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -675,39 +669,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Santa Maria Tex Mex</t>
+          <t>Xtra pasta, Xtra tun eller Coop hakkede tomater</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa</t>
+          <t>Xtra</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>28-371 g</t>
+          <t>56-500 g</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>356,43. kr/kg</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>89,29. kr/kg</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1029963</t>
+          <t>1029964</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F861403ff8278bc91605620bb5efbd9a3&amp;w=552&amp;s=d7a80a2643a317b9b8c74e45a97f2fa6</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6bc716e15b0f10599682a3d3741f4d5b&amp;w=552&amp;s=492d4884a5bdd6f92a5aedef9dee462f</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>e1ce6e721dc92236</t>
+          <t>cb96656d30393173</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -715,7 +711,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -725,41 +725,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Xtra pasta, Xtra tun eller Coop hakkede tomater</t>
+          <t>Riberhus skæreost</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Xtra</t>
+          <t>Riberhus</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>56-500 g</t>
+          <t>. 430 g</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>89,29. kr/kg</t>
+          <t>90,70. kr/kg</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1029964</t>
+          <t>1029965</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6bc716e15b0f10599682a3d3741f4d5b&amp;w=552&amp;s=492d4884a5bdd6f92a5aedef9dee462f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5932c78cfeea5c479b539338e154b8d9%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc4b8b92b2f71cb39a7a3b7a88fb78804&amp;w=252&amp;s=38ad91aa0ea56e2278575a32bc5400f1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>cb96656d30393173</t>
+          <t>d0e26b602e93e61f</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -781,41 +781,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Riberhus skæreost</t>
+          <t>Kims chips store poser</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Riberhus</t>
+          <t>Kims</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>. 430 g</t>
+          <t>210-255 g</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>90,70. kr/kg</t>
+          <t>92,68. kr/kg</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1029965</t>
+          <t>1029907</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5932c78cfeea5c479b539338e154b8d9%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc4b8b92b2f71cb39a7a3b7a88fb78804&amp;w=252&amp;s=38ad91aa0ea56e2278575a32bc5400f1</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F12a98cf38afdad299576a24a23a52989%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe70ca024eab4787fd3f65acdeb70edfb%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2459a775c9e7191a869e3bab4cc69e91&amp;w=552&amp;s=52ca159560db146247bf8a2f9f5464c5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>d0e26b602e93e61f</t>
+          <t>d6f56b4a310439e9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -837,41 +837,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kims chips store poser</t>
+          <t>Coop Italiana pizza</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kims</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>210-255 g</t>
+          <t>300-360 g</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>92,68. kr/kg</t>
+          <t>66,67. kr/kg</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1029907</t>
+          <t>1029908</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F12a98cf38afdad299576a24a23a52989%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe70ca024eab4787fd3f65acdeb70edfb%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2459a775c9e7191a869e3bab4cc69e91&amp;w=552&amp;s=52ca159560db146247bf8a2f9f5464c5</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9dac8d93868ba0c9fc905c59fe69b45f%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7a4588ff8fb4e59586cedc36394a2da6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2c88dbc5246da334483449f3df363aae&amp;w=552&amp;s=dc13902ffdb5da9afd50ee303f60ce35</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>d6f56b4a310439e9</t>
+          <t>a92354dc334eb563</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1 pose</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -893,41 +893,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Coop Italiana pizza</t>
+          <t>Carte D´or is eller Marabou ispinde</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Carte</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>300-360 g</t>
+          <t>270-1000 ml</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>66,67. kr/kg</t>
+          <t>129,63. kr/l</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1029908</t>
+          <t>1029909</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9dac8d93868ba0c9fc905c59fe69b45f%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7a4588ff8fb4e59586cedc36394a2da6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2c88dbc5246da334483449f3df363aae&amp;w=552&amp;s=dc13902ffdb5da9afd50ee303f60ce35</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=203&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fefef182a02092b1520afe7aa3e46204b&amp;w=252&amp;s=5d57f17cb1f8bfdbb8e0028dbeef08b2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>a92354dc334eb563</t>
+          <t>91c66a9b669d3b42</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -949,41 +949,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Carte D´or is eller Marabou ispinde</t>
+          <t>Canaja Gold eller Clarkson</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Carte</t>
+          <t>Canaja</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>270-1000 ml</t>
+          <t>75 cl</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>129,63. kr/l</t>
+          <t>66,67. kr/l</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1029909</t>
+          <t>1029910</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=203&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fefef182a02092b1520afe7aa3e46204b&amp;w=252&amp;s=5d57f17cb1f8bfdbb8e0028dbeef08b2</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=203&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0273aff80f9d53eb78fef5929ba20393&amp;w=252&amp;s=2acbba1dc763d3fdf0db7b5d1837d957</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>91c66a9b669d3b42</t>
+          <t>c76c319339962c67</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -1005,41 +1005,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Canaja Gold eller Clarkson</t>
+          <t>Gøl pølser</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canaja</t>
+          <t>Gøl</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>630-750 g</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>66,67. kr/l</t>
+          <t>71,43. kr/kg</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1029910</t>
+          <t>1048016</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=203&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0273aff80f9d53eb78fef5929ba20393&amp;w=252&amp;s=2acbba1dc763d3fdf0db7b5d1837d957</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7ff55840c833c75068caaf6ee5a42e63&amp;w=552&amp;s=8175dcacd9dd36d951c09df8921e07dd</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>c76c319339962c67</t>
+          <t>cc600ebf1b84669f</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -1061,41 +1061,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gøl pølser</t>
+          <t>Ben &amp; Jerry´s is</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gøl</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>630-750 g</t>
+          <t>465 ml</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>71,43. kr/kg</t>
+          <t>83,87. kr/l</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1048016</t>
+          <t>1048017</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7ff55840c833c75068caaf6ee5a42e63&amp;w=552&amp;s=8175dcacd9dd36d951c09df8921e07dd</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F243aad5da6534e9b2317a532184cea34%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb89a47c60c36f53a78edd0ba5ee5c769%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fee9b9b0fc33110e6c08f019845295cf8&amp;w=552&amp;s=d5f33cd40a30d05d09f39a2fd18b8fac</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>cc600ebf1b84669f</t>
+          <t>f80e07f15aa0b79c</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -1117,41 +1117,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ben &amp; Jerry´s is</t>
+          <t>1664, Breezer, Somersby eller Red Bull</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>1664,</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>465 ml</t>
+          <t>25-33 cl</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>83,87. kr/l</t>
+          <t>44,00 kr/l</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1048017</t>
+          <t>1048019</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F243aad5da6534e9b2317a532184cea34%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb89a47c60c36f53a78edd0ba5ee5c769%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fee9b9b0fc33110e6c08f019845295cf8&amp;w=552&amp;s=d5f33cd40a30d05d09f39a2fd18b8fac</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F94941b930f8cdd0e161e146fe29690fe&amp;w=252&amp;s=a2785839ca2e9255a8cf10fe124d688d</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>f80e07f15aa0b79c</t>
+          <t>8dd2302e773b5a31</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 dåse/flaske</t>
         </is>
       </c>
     </row>
@@ -1173,41 +1173,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1664, Breezer, Somersby eller Red Bull</t>
+          <t>Royal Classic eller Pilsner, Odense Classic, Faxe Kondi Booster, Pepsi Max eller Faxe Kondi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1664,</t>
+          <t>Royal</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>25-33 cl</t>
+          <t>8 x 50 cl</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>44,00 kr/l</t>
+          <t>19,75 kr/l</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1048019</t>
+          <t>1048018</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F94941b930f8cdd0e161e146fe29690fe&amp;w=252&amp;s=a2785839ca2e9255a8cf10fe124d688d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=183&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F352f4ece95420faacd9d290af0e5d3ba&amp;w=252&amp;s=490a6b7073c1651992bfdcc3482cd452</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8dd2302e773b5a31</t>
+          <t>92c1393a6bc66679</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1 dåse/flaske</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -1229,41 +1229,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Royal Classic eller Pilsner, Odense Classic, Faxe Kondi Booster, Pepsi Max eller Faxe Kondi</t>
+          <t>Xtra kyllingebryst eller -inderfilet</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Royal</t>
+          <t>Xtra</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8 x 50 cl</t>
+          <t>600 g</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19,75 kr/l</t>
+          <t>81,67. kr/kg</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1048018</t>
+          <t>1043648</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=183&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F352f4ece95420faacd9d290af0e5d3ba&amp;w=252&amp;s=490a6b7073c1651992bfdcc3482cd452</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9751d328ddbe09d3da2523b802dbadbb%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa86d0b8b5fd11fb3113e1eeb242fbf6b&amp;w=752&amp;s=89ab5e0469862f098aabbc6cf0e1a445</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>92c1393a6bc66679</t>
+          <t>c0e01fce7a644e2f</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Xtra kyllingebryst eller -inderfilet</t>
+          <t>Xtra hel kylling</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1295,31 +1295,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>600 g</t>
+          <t>1450 g</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>81,67. kr/kg</t>
+          <t>37,93. kr/kg</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1043648</t>
+          <t>1029914</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9751d328ddbe09d3da2523b802dbadbb%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa86d0b8b5fd11fb3113e1eeb242fbf6b&amp;w=752&amp;s=89ab5e0469862f098aabbc6cf0e1a445</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F95e444724e8cd27b4d3504a329627bc6&amp;w=352&amp;s=92b221ef6a043999ffeef81d4bb2eb95</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>c0e01fce7a644e2f</t>
+          <t>d0072be9371c5373</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -1341,41 +1341,41 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Xtra hel kylling</t>
+          <t>Coop stegeflæsk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Xtra</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1450 g</t>
+          <t>500 g</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>37,93. kr/kg</t>
+          <t>98,00. kr/kg</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1029914</t>
+          <t>1029912</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F95e444724e8cd27b4d3504a329627bc6&amp;w=352&amp;s=92b221ef6a043999ffeef81d4bb2eb95</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F54a0e5a0f6291272ea5c310ab807debf&amp;w=352&amp;s=7dea98c5ef72a691c99355d335cc6785</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>d0072be9371c5373</t>
+          <t>ea7a15b542f21553</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -1397,41 +1397,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Coop stegeflæsk</t>
+          <t>Dansk Kalv entrecote eller ribeye</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Dansk</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>500 g</t>
+          <t>350 g</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>98,00. kr/kg</t>
+          <t>282,86. kr/kg</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1029912</t>
+          <t>1029911</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F54a0e5a0f6291272ea5c310ab807debf&amp;w=352&amp;s=7dea98c5ef72a691c99355d335cc6785</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8ffb5fbcc1ca0fe7443880ede1b148a3%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F502850b35cdec1e51ce717d700365acb&amp;w=352&amp;s=10d48f0bfb6f5f2a069f8fd9e5fec85d</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>ea7a15b542f21553</t>
+          <t>dcff01a0261bb276</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1453,41 +1453,41 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dansk Kalv entrecote eller ribeye</t>
+          <t>Irma Vitendo tomater</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dansk</t>
+          <t>Irma</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>350 g</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>282,86. kr/kg</t>
+          <t>55,00. kr/kg</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1029911</t>
+          <t>1029918</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8ffb5fbcc1ca0fe7443880ede1b148a3%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F502850b35cdec1e51ce717d700365acb&amp;w=352&amp;s=10d48f0bfb6f5f2a069f8fd9e5fec85d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9214c0637e5db88b766d162f2be5cdba&amp;w=552&amp;s=81c93905c259ad73b5f08324b3368724</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>dcff01a0261bb276</t>
+          <t>cce61913663956d5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 bakke</t>
         </is>
       </c>
     </row>
@@ -1509,22 +1509,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Irma Vitendo tomater</t>
+          <t>Pink Lady æbler</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Pink</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>8 stk</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>55,00. kr/kg</t>
+          <t>2,75. kr/stk</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1533,17 +1533,17 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1029918</t>
+          <t>1043649</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9214c0637e5db88b766d162f2be5cdba&amp;w=552&amp;s=81c93905c259ad73b5f08324b3368724</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa58a25726c5bb867b1e32ab86c6316f6&amp;w=552&amp;s=dd89410f9e931d26fc8f62461cabebb9</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>cce61913663956d5</t>
+          <t>c19436cd52776972</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1565,41 +1565,41 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pink Lady æbler</t>
+          <t>Ærter</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pink</t>
+          <t>Ærter</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8 stk</t>
+          <t>500 g</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2,75. kr/stk</t>
+          <t>50,00. kr/kg</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1043649</t>
+          <t>1029917</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa58a25726c5bb867b1e32ab86c6316f6&amp;w=552&amp;s=dd89410f9e931d26fc8f62461cabebb9</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faa4b6670043f8e6e8b76df04e3e4389d&amp;w=252&amp;s=730603d93a6eb1aadd3f4a2423e00f86</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>c19436cd52776972</t>
+          <t>95c992b6cb980eb6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1621,41 +1621,41 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ærter</t>
+          <t>Danske frilandsæg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ærter</t>
+          <t>Danske</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>500 g</t>
+          <t>10 stk</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>50,00. kr/kg</t>
+          <t>2,60. kr/stk</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1029917</t>
+          <t>1029921</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faa4b6670043f8e6e8b76df04e3e4389d&amp;w=252&amp;s=730603d93a6eb1aadd3f4a2423e00f86</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbe29c136be04a69154119eb4a7a28207&amp;w=552&amp;s=a21c629effca5989fb023403dfa3bc29</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>95c992b6cb980eb6</t>
+          <t>ca4a3595ea6ac4b5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1677,41 +1677,41 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Danske frilandsæg</t>
+          <t>Danonino eller Actimel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Danske</t>
+          <t>Danonino</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10 stk</t>
+          <t>4x100 g</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2,60. kr/stk</t>
+          <t>50,00. kr/kg</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1029921</t>
+          <t>1029922</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbe29c136be04a69154119eb4a7a28207&amp;w=552&amp;s=a21c629effca5989fb023403dfa3bc29</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffe8aade644a503007faa67ab0f42fda4%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdab11231f196434fb9d951e44dc1c3be&amp;w=552&amp;s=ba6f9921e2931e0a70c92dbfcf1196db</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>ca4a3595ea6ac4b5</t>
+          <t>9533330e39d4cce6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1 bakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -1733,41 +1733,41 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Danonino eller Actimel</t>
+          <t>Puck ost</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Danonino</t>
+          <t>Puck</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4x100 g</t>
+          <t>200 g</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>50,00. kr/kg</t>
+          <t>90,00. kr/kg</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1029922</t>
+          <t>1029920</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffe8aade644a503007faa67ab0f42fda4%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdab11231f196434fb9d951e44dc1c3be&amp;w=552&amp;s=ba6f9921e2931e0a70c92dbfcf1196db</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1ffeb33b14cf1ce714b561ec1254af80&amp;w=232&amp;s=d747b0b09b3bbd85a197723e652a54a5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>9533330e39d4cce6</t>
+          <t>82b3670eb94b3734</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1789,43 +1789,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Puck ost</t>
+          <t>Dagmartærte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Puck</t>
+          <t>Dagmartærte</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>200 g</t>
+          <t>1 stk</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>90,00. kr/kg</t>
+          <t>30,00. kr/stk</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1029920</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1ffeb33b14cf1ce714b561ec1254af80&amp;w=232&amp;s=d747b0b09b3bbd85a197723e652a54a5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>82b3670eb94b3734</t>
-        </is>
-      </c>
+          <t>1029919</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -1845,35 +1837,43 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dagmartærte</t>
+          <t>Graasten kartoffelsalat</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dagmartærte</t>
+          <t>Graasten</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1 stk</t>
+          <t>800 g</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>30,00. kr/stk</t>
+          <t>31,25. kr/kg</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1029919</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>1029923</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F52bdd36aeb9c4864ca69067c8e5dee2c&amp;w=552&amp;s=054938ab32135b0cdce1f94cc2f28eed</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>90391b66cecccec9</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -1893,41 +1893,41 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Graasten kartoffelsalat</t>
+          <t>Langelænder pølser</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Graasten</t>
+          <t>Langelænder</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>800 g</t>
+          <t>325-360 g</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>31,25. kr/kg</t>
+          <t>89,23. kr/kg</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1029923</t>
+          <t>1029924</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F52bdd36aeb9c4864ca69067c8e5dee2c&amp;w=552&amp;s=054938ab32135b0cdce1f94cc2f28eed</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb4c4e33e0c7e682696281fe491faceb9%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F063e68ae8d1b5b4ca16fe29584c62c9c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa190d6311262bd3cc9bd7e2b5e27e703&amp;w=552&amp;s=31400bd75dbfa916c067e90fbbf5b520</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>90391b66cecccec9</t>
+          <t>83a1561e395ae4e7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -1949,41 +1949,41 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Langelænder pølser</t>
+          <t>Pågen brød</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Langelænder</t>
+          <t>Pågen</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>325-360 g</t>
+          <t>650-900 g</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>89,23. kr/kg</t>
+          <t>30,77. kr/kg</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1029924</t>
+          <t>1029925</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb4c4e33e0c7e682696281fe491faceb9%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F063e68ae8d1b5b4ca16fe29584c62c9c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa190d6311262bd3cc9bd7e2b5e27e703&amp;w=552&amp;s=31400bd75dbfa916c067e90fbbf5b520</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2f34c919c36beb31fbd04735bc4d1849%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fffb4ac0a867e103689274ee2eea247c9&amp;w=1152&amp;s=45c6ff12b7a0ac9c4c2b6b8dbc37c748</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>83a1561e395ae4e7</t>
+          <t>99e0661d772bb234</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2005,41 +2005,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pågen brød</t>
+          <t>Citterio bresaola, mortadella, prosciutto cotto, salame di milano eller prosciutto crudo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pågen</t>
+          <t>Citterio</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>650-900 g</t>
+          <t>70-125 g</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>30,77. kr/kg</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>20</v>
-      </c>
+          <t>257,14. kr/kg</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1029925</t>
+          <t>1053686</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2f34c919c36beb31fbd04735bc4d1849%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fffb4ac0a867e103689274ee2eea247c9&amp;w=1152&amp;s=45c6ff12b7a0ac9c4c2b6b8dbc37c748</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F007794443d65e8427bab2a53bb0b2f79&amp;w=552&amp;s=39db8ee0db7c5475d1abbd1e841d2790</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>99e0661d772bb234</t>
+          <t>cf8e64ce30cc31ce</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2047,11 +2045,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>1 pakke</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2061,39 +2055,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Citterio bresaola, mortadella, prosciutto cotto, salame di milano eller prosciutto crudo</t>
+          <t>Hele kyllingelår eller hakket gris/kalv 8-12%</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Citterio</t>
+          <t>Hele</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>70-125 g</t>
+          <t>900-2000 g</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>257,14. kr/kg</t>
+          <t>76,67. kr/kg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1053686</t>
+          <t>1053687</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F007794443d65e8427bab2a53bb0b2f79&amp;w=552&amp;s=39db8ee0db7c5475d1abbd1e841d2790</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F90565b931b1f9ce20e91a2bbeea07a2c&amp;w=552&amp;s=ce81ba4f3c26f9d7e781b4bf0f4905fe</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>cf8e64ce30cc31ce</t>
+          <t>da183ec769c6326c</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2111,39 +2105,41 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hele kyllingelår eller hakket gris/kalv 8-12%</t>
+          <t>Thise økologisk koldskål</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hele</t>
+          <t>Thise</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>900-2000 g</t>
+          <t>1 l</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>76,67. kr/kg</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>20,00. kr/l</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>20</v>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1053687</t>
+          <t>1029926</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F90565b931b1f9ce20e91a2bbeea07a2c&amp;w=552&amp;s=ce81ba4f3c26f9d7e781b4bf0f4905fe</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1191b4a28c259eede8b400cc53cdb27f&amp;w=552&amp;s=e4bdbf92220720b9d9bb6916376e6028</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>da183ec769c6326c</t>
+          <t>90e3e32d3f199992</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2151,7 +2147,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Thise økologisk koldskål</t>
+          <t>Thise økologisk tapas- eller skiveost</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2171,31 +2171,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1 l</t>
+          <t>. 180 g</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20,00. kr/l</t>
+          <t>138,89. kr/kg</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1029926</t>
+          <t>1029928</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1191b4a28c259eede8b400cc53cdb27f&amp;w=552&amp;s=e4bdbf92220720b9d9bb6916376e6028</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5c2e13260343dfef6baa99c109799cb1&amp;w=552&amp;s=11b3c21136c0ac9ad9df7f64b476b049</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>90e3e32d3f199992</t>
+          <t>9b9239c63193cb3c</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 stk./pakke</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Thise økologisk tapas- eller skiveost</t>
+          <t>Thise økologisk vesterhavs- eller midsommerost</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2227,31 +2227,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>. 180 g</t>
+          <t>. 225 g</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>138,89. kr/kg</t>
+          <t>200,00. kr/kg</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1029928</t>
+          <t>1029929</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5c2e13260343dfef6baa99c109799cb1&amp;w=552&amp;s=11b3c21136c0ac9ad9df7f64b476b049</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=203&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F93304d585ce4f25ae44fe296a83846f2&amp;w=252&amp;s=76b45c2c6ba5fc8498845624ba0fa457</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>9b9239c63193cb3c</t>
+          <t>81b1679333c137ce</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1 stk./pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Thise økologisk vesterhavs- eller midsommerost</t>
+          <t>Thise økologisk aktiv drikkeyoghurt eller proteindrik</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2283,31 +2283,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>. 225 g</t>
+          <t>300 ml</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>200,00. kr/kg</t>
+          <t>33,33. kr/l</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1029929</t>
+          <t>1029930</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=203&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F93304d585ce4f25ae44fe296a83846f2&amp;w=252&amp;s=76b45c2c6ba5fc8498845624ba0fa457</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=202&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0a86961c51e7aad861c836afd029a06a&amp;w=252&amp;s=d73890276f4441018a0a0b8113a05734</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>81b1679333c137ce</t>
+          <t>9085a79c2c9d2ddb</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Thise økologisk aktiv drikkeyoghurt eller proteindrik</t>
+          <t>Thise dansk økologisk smør eller smørbart</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2339,31 +2339,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>300 ml</t>
+          <t>200 g</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>33,33. kr/l</t>
+          <t>100,00. kr/kg</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1029930</t>
+          <t>1029927</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=202&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0a86961c51e7aad861c836afd029a06a&amp;w=252&amp;s=d73890276f4441018a0a0b8113a05734</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa1b4a540c1366ae9fd43bba9e3db3d06&amp;w=451&amp;s=453fd7112f5758e2e039dd6710857bbc</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>9085a79c2c9d2ddb</t>
+          <t>8a533f2b212d3d74</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -2385,41 +2385,41 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Thise dansk økologisk smør eller smørbart</t>
+          <t>Xtra røget laks eller rejer</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thise</t>
+          <t>Xtra</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>200 g</t>
+          <t>100-170 g</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>100,00. kr/kg</t>
+          <t>280,00. kr/kg</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1029927</t>
+          <t>1029931</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa1b4a540c1366ae9fd43bba9e3db3d06&amp;w=451&amp;s=453fd7112f5758e2e039dd6710857bbc</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe68c805f346b8c8aebfb091b5fd30982&amp;w=552&amp;s=908ea869275d4036e251f13fbf51996d</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>8a533f2b212d3d74</t>
+          <t>860f77f860327f60</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -2441,41 +2441,41 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Xtra røget laks eller rejer</t>
+          <t>Änglamark økologisk fettucine</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Xtra</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>100-170 g</t>
+          <t>250 g</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>280,00. kr/kg</t>
+          <t>56,00. kr/kg</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1029931</t>
+          <t>1029933</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe68c805f346b8c8aebfb091b5fd30982&amp;w=552&amp;s=908ea869275d4036e251f13fbf51996d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2901372cdcae4475761eb5f323ebbbb8%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2261073b3077e0b47e51da3808aec901&amp;w=552&amp;s=ce1b6196ae50a4e8c8dba8d2d11dc557</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>860f77f860327f60</t>
+          <t>93943b393c933cc3</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -2497,41 +2497,41 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Änglamark økologisk fettucine</t>
+          <t>Graasten pålægssalat</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Graasten</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>250 g</t>
+          <t>120 g</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>56,00. kr/kg</t>
+          <t>100,00. kr/kg</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1029933</t>
+          <t>1029932</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2901372cdcae4475761eb5f323ebbbb8%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2261073b3077e0b47e51da3808aec901&amp;w=552&amp;s=ce1b6196ae50a4e8c8dba8d2d11dc557</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe78369c41e3668d747a9a4d7560a619f%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd79bce153cf7e878528edd3983a7ed97%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1db13c30db81dd87f1fe404bb36b0918&amp;w=552&amp;s=90af376518f26a28ce3417477f7b452d</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>93943b393c933cc3</t>
+          <t>d7e632036c1c395b</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1 pose</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -2553,41 +2553,41 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Graasten pålægssalat</t>
+          <t>Coop Kylling</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Graasten</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>120 g</t>
+          <t>750-1500 g</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>100,00. kr/kg</t>
+          <t>50,67. kr/kg</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1029932</t>
+          <t>1029934</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe78369c41e3668d747a9a4d7560a619f%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd79bce153cf7e878528edd3983a7ed97%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1db13c30db81dd87f1fe404bb36b0918&amp;w=552&amp;s=90af376518f26a28ce3417477f7b452d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F25f7d84484d16cb33ccea0ff03c6d5f0%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc1e84544869fd363dfae125fc838dccd%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8b289f68bfe8ed55c48973db006b5af9&amp;w=552&amp;s=338722ac036e7a5a1efa74f5bd49779c</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>d7e632036c1c395b</t>
+          <t>9d11ec9392db811f</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Coop Kylling</t>
+          <t>Coop Asia cubes</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2619,31 +2619,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>750-1500 g</t>
+          <t>350 g</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>50,67. kr/kg</t>
+          <t>71,43. kr/kg</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1029934</t>
+          <t>1029935</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F25f7d84484d16cb33ccea0ff03c6d5f0%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc1e84544869fd363dfae125fc838dccd%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8b289f68bfe8ed55c48973db006b5af9&amp;w=552&amp;s=338722ac036e7a5a1efa74f5bd49779c</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F280e43edcf8e62d431049ed95d733b70%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F26b7b75aadf0e67a2f9a502ff6bc16b9&amp;w=552&amp;s=8816194d5eea16d8e5c411b15f851fd6</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>9d11ec9392db811f</t>
+          <t>b02d913d77966e18</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Coop Asia cubes</t>
+          <t>Coop sprøde fiskeportioner eller fiskefileter</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2675,31 +2675,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>350 g</t>
+          <t>200-500 g</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>71,43. kr/kg</t>
+          <t>160,00. kr/kg</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1029935</t>
+          <t>1029936</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F280e43edcf8e62d431049ed95d733b70%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F26b7b75aadf0e67a2f9a502ff6bc16b9&amp;w=552&amp;s=8816194d5eea16d8e5c411b15f851fd6</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=203&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9b5307ebb1c67a323983df2e500feb4c&amp;w=252&amp;s=95351122829f983d45c815fa11c7bed5</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>b02d913d77966e18</t>
+          <t>95c64e9d6ae94a8c</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2721,41 +2721,41 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Coop sprøde fiskeportioner eller fiskefileter</t>
+          <t>Steff Houlberg maxiretter</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Steff</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>200-500 g</t>
+          <t>450 g</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>160,00. kr/kg</t>
+          <t>77,78. kr/kg</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1029936</t>
+          <t>1029937</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=203&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9b5307ebb1c67a323983df2e500feb4c&amp;w=252&amp;s=95351122829f983d45c815fa11c7bed5</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb7bf10eb54f1f2d42ce8607294948109%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F84917c959e63229c0113c7564a5ef9b2%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F411f51535426f6b993c4389b6569c4b7&amp;w=252&amp;s=91c9e882ed14c085f9d88117182d0d78</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>95c64e9d6ae94a8c</t>
+          <t>93e65e99250b2d74</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -2777,41 +2777,41 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Steff Houlberg maxiretter</t>
+          <t>Heinz ketchup eller mayonnaise</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Steff</t>
+          <t>Heinz</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>450 g</t>
+          <t>395-570 g</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>77,78. kr/kg</t>
+          <t>50,63. kr/kg</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1029937</t>
+          <t>1029942</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb7bf10eb54f1f2d42ce8607294948109%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F84917c959e63229c0113c7564a5ef9b2%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F411f51535426f6b993c4389b6569c4b7&amp;w=252&amp;s=91c9e882ed14c085f9d88117182d0d78</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Feb4e3ba7546b85d7dd58d4651e8aa540%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa9046d8d0f3b672c029faf99ef944302&amp;w=552&amp;s=22e8c3f22ed379d7e2fe8cf14183e504</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>93e65e99250b2d74</t>
+          <t>912972e27e626e6a</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -2833,41 +2833,41 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Heinz ketchup eller mayonnaise</t>
+          <t>Santagata olivenolie</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Heinz</t>
+          <t>Santagata</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>395-570 g</t>
+          <t>1 L</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>50,63. kr/kg</t>
+          <t>79,00. kr/l</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1029942</t>
+          <t>1029941</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Feb4e3ba7546b85d7dd58d4651e8aa540%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa9046d8d0f3b672c029faf99ef944302&amp;w=552&amp;s=22e8c3f22ed379d7e2fe8cf14183e504</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F12db856b65b917f403f5c87db912e2b4&amp;w=95&amp;s=efe9134c633f21b5b89808b56915f0ee</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>912972e27e626e6a</t>
+          <t>f6070ece1ff41898</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -2889,41 +2889,41 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Santagata olivenolie</t>
+          <t>OTA solgryn</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Santagata</t>
+          <t>OTA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1 L</t>
+          <t>700 g</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>79,00. kr/l</t>
+          <t>17,14. kr/kg</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1029941</t>
+          <t>1029939</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F12db856b65b917f403f5c87db912e2b4&amp;w=95&amp;s=efe9134c633f21b5b89808b56915f0ee</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F82d642042711f4691600acd343a21fa0&amp;w=252&amp;s=33514fd82fe1636c03ee57a341bd6e9e</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>f6070ece1ff41898</t>
+          <t>c3c3b69a6c689699</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -2945,41 +2945,41 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OTA solgryn</t>
+          <t>Den Gamle Fabrik marmelade</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OTA</t>
+          <t>Den</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>700 g</t>
+          <t>350-425 g</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>17,14. kr/kg</t>
+          <t>82,86. kr/kg</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1029939</t>
+          <t>1029938</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F82d642042711f4691600acd343a21fa0&amp;w=252&amp;s=33514fd82fe1636c03ee57a341bd6e9e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb920ddc82de2121237ae5aac5f3805f8%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4047a7519f07132162425d0e9643c85b%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9091c8c2c3ef6a0cd9ecd87b9c71dcd0%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3d83eefc8119773dfcbe3277046f38d1&amp;w=252&amp;s=f2e240008ccb9f9cb0c13864d192f298</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>c3c3b69a6c689699</t>
+          <t>c5783a86fc5b8724</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -3001,41 +3001,41 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Den Gamle Fabrik marmelade</t>
+          <t>Valsemøllen kage-, brødblanding eller sukker</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Den</t>
+          <t>Valsemøllen</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>350-425 g</t>
+          <t>400-2000 g</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>82,86. kr/kg</t>
+          <t>42,50. kr/kg</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1029938</t>
+          <t>1029940</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb920ddc82de2121237ae5aac5f3805f8%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4047a7519f07132162425d0e9643c85b%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9091c8c2c3ef6a0cd9ecd87b9c71dcd0%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3d83eefc8119773dfcbe3277046f38d1&amp;w=252&amp;s=f2e240008ccb9f9cb0c13864d192f298</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F579b32a002ffa91cd94d35b2d784320d&amp;w=316&amp;s=d00bd7da909fbc12106dc8520a159322</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>c5783a86fc5b8724</t>
+          <t>84e245f97f91207d</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -3057,41 +3057,41 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Valsemøllen kage-, brødblanding eller sukker</t>
+          <t>Ritter Sport</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Valsemøllen</t>
+          <t>Ritter</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>400-2000 g</t>
+          <t>100 g</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>42,50. kr/kg</t>
+          <t>200,00. kr/kg</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1029940</t>
+          <t>1029946</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F579b32a002ffa91cd94d35b2d784320d&amp;w=316&amp;s=d00bd7da909fbc12106dc8520a159322</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4245946243abb7db1469ac185c1e0f4f&amp;w=552&amp;s=ed3559f0521ca59392b057099d4bf2b1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>84e245f97f91207d</t>
+          <t>d54f088d38e6363b</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -3113,41 +3113,41 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ritter Sport</t>
+          <t>Sun Lolly</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ritter</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>100 g</t>
+          <t>8 x 60 ml</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>200,00. kr/kg</t>
+          <t>33,33. kr/l</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1029946</t>
+          <t>1029944</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4245946243abb7db1469ac185c1e0f4f&amp;w=552&amp;s=ed3559f0521ca59392b057099d4bf2b1</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2d2ca6d7211333213152f539af36de40%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0e2162e38a5aff5c21383b1b1f0471ec%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5ec9e01846238e9e7460635c83b53d68&amp;w=552&amp;s=858f334f6d70b5d8c1d8e21aa0bc605d</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>d54f088d38e6363b</t>
+          <t>bc09c17649a93fcc</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -3169,41 +3169,41 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sun Lolly</t>
+          <t>Dan Cake kager</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8 x 60 ml</t>
+          <t>350 g</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>33,33. kr/l</t>
+          <t>57,14. kr/kg</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1029944</t>
+          <t>1029945</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2d2ca6d7211333213152f539af36de40%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0e2162e38a5aff5c21383b1b1f0471ec%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5ec9e01846238e9e7460635c83b53d68&amp;w=552&amp;s=858f334f6d70b5d8c1d8e21aa0bc605d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffc88036ec376034b8bc623e14377eb51%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8eea49fff56a0ba124c3c51e04e79ed1%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6b2a77a1e8a32e51d032f3bfc999b116&amp;w=252&amp;s=6984359bdbbc2651f6cc1a5afb5edb67</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>bc09c17649a93fcc</t>
+          <t>c05e57912e0d6fb4</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3225,41 +3225,41 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dan Cake kager</t>
+          <t>BKI eller Karat formalet kaffe</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>BKI</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>350 g</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>57,14. kr/kg</t>
+          <t>112,50. kr/kg</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1029945</t>
+          <t>1029943</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffc88036ec376034b8bc623e14377eb51%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8eea49fff56a0ba124c3c51e04e79ed1%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6b2a77a1e8a32e51d032f3bfc999b116&amp;w=252&amp;s=6984359bdbbc2651f6cc1a5afb5edb67</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7e504201259ba8d8d71b46120ea34564%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F77ed713a8ebae73f982c2aa82ddc7ff4&amp;w=252&amp;s=bbf4710133f218d0113c7b0f55537eab</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>c05e57912e0d6fb4</t>
+          <t>911f3e616d996952</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -3281,41 +3281,45 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BKI eller Karat formalet kaffe</t>
+          <t>McHogan's i boks</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BKI</t>
+          <t>McHogan's</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>3 l</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>112,50. kr/kg</t>
+          <t>33,00. kr/l</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>45</v>
-      </c>
-      <c r="G52" t="inlineStr"/>
+        <v>99</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>119.95.</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1029943</t>
+          <t>1029950</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7e504201259ba8d8d71b46120ea34564%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F77ed713a8ebae73f982c2aa82ddc7ff4&amp;w=252&amp;s=bbf4710133f218d0113c7b0f55537eab</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F411987ccc8f9e74bfc86fe3fd421aa38%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa4d99dbea927ff016a64ce72db4e2b55%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3ed984309958ce778024c9475e572286&amp;w=552&amp;s=a253fe9efe0aee661df4b12b6aa80b79</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>911f3e616d996952</t>
+          <t>8fb0704f65cea8b2</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3325,7 +3329,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1 pose</t>
+          <t>1 boks</t>
         </is>
       </c>
     </row>
@@ -3337,45 +3341,41 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>McHogan's i boks</t>
+          <t>Cuvée Dissenay eller Piccini Chianti Riserva</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>McHogan's</t>
+          <t>Cuvée</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3 l</t>
+          <t>75 cl</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>33,00. kr/l</t>
+          <t>66,67. kr/l</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>99</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>119.95.</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1029950</t>
+          <t>1029947</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F411987ccc8f9e74bfc86fe3fd421aa38%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa4d99dbea927ff016a64ce72db4e2b55%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3ed984309958ce778024c9475e572286&amp;w=552&amp;s=a253fe9efe0aee661df4b12b6aa80b79</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8c259b38d48b44c959afb7943e7dea71&amp;w=552&amp;s=fbf301f650f3cbdae1dbf2db614224ac</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>8fb0704f65cea8b2</t>
+          <t>8c33cccd33cc33cc</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1 boks</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -3397,12 +3397,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cuvée Dissenay eller Piccini Chianti Riserva</t>
+          <t>Spier Note eller Piquitos Moscato</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cuvée</t>
+          <t>Spier</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3412,26 +3412,26 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>66,67. kr/l</t>
+          <t>53,33. kr/l</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1029947</t>
+          <t>1029948</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8c259b38d48b44c959afb7943e7dea71&amp;w=552&amp;s=fbf301f650f3cbdae1dbf2db614224ac</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=203&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7714400e656e2b52cf2a33d31579802b%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9c4afbcd2c5db591056a074c93182ba8%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffb5926e2b98b5c93a4077243b0e49e99&amp;w=252&amp;s=580f705c7a2a22f99e0fee66e9ef7d1c</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>8c33cccd33cc33cc</t>
+          <t>c13a36b649a63bc9</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3453,41 +3453,45 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Spier Note eller Piquitos Moscato</t>
+          <t>Viña Maipo i boks</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spier</t>
+          <t>Viña</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>3 l</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>53,33. kr/l</t>
+          <t>39,67. kr/l</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>40</v>
-      </c>
-      <c r="G55" t="inlineStr"/>
+        <v>119</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>129.95.</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1029948</t>
+          <t>1029949</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=203&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7714400e656e2b52cf2a33d31579802b%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9c4afbcd2c5db591056a074c93182ba8%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffb5926e2b98b5c93a4077243b0e49e99&amp;w=252&amp;s=580f705c7a2a22f99e0fee66e9ef7d1c</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5f7c5733da0033e0cc7955132f303b3d&amp;w=252&amp;s=9930277a698b3f0958937d94e17f6c45</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>c13a36b649a63bc9</t>
+          <t>95336ac46ce435e5</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3497,7 +3501,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 boks</t>
         </is>
       </c>
     </row>
@@ -3509,45 +3513,41 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Viña Maipo i boks</t>
+          <t>Bread &amp; Butter eller Terrunyo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Viña</t>
+          <t>Bread</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3 l</t>
+          <t>75 cl</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>39,67. kr/l</t>
+          <t>132,00. kr/l</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>119</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>129.95.</t>
-        </is>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1029949</t>
+          <t>1029954</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5f7c5733da0033e0cc7955132f303b3d&amp;w=252&amp;s=9930277a698b3f0958937d94e17f6c45</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5dd89b35680a0c14456e21ee6fde279c&amp;w=552&amp;s=83b0b2f4601701699aaca4c9e6d715ba</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>95336ac46ce435e5</t>
+          <t>d83763a51ec80fca</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1 boks</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bread &amp; Butter eller Terrunyo</t>
+          <t>Faustino V Reserva eller Exhib' Rosé</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bread</t>
+          <t>Faustino</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3584,26 +3584,26 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>132,00. kr/l</t>
+          <t>78,67. kr/l</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1029954</t>
+          <t>1029952</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5dd89b35680a0c14456e21ee6fde279c&amp;w=552&amp;s=83b0b2f4601701699aaca4c9e6d715ba</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3dc1efe4122a403859f2991d6cb80269&amp;w=152&amp;s=c4b64e7c351dc417d537a40b33dc2d8f</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>d83763a51ec80fca</t>
+          <t>b04b46bc38cc6bcb</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 flasker</t>
         </is>
       </c>
     </row>
@@ -3625,41 +3625,41 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Faustino V Reserva eller Exhib' Rosé</t>
+          <t>Fernet-Branca Bitter, Linie Aquavit eller Nordguld Akvavit</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Faustino</t>
+          <t>Fernet-Branca</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>70 cl</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>78,67. kr/l</t>
+          <t>200,00. kr/l</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1029952</t>
+          <t>1029951</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3dc1efe4122a403859f2991d6cb80269&amp;w=152&amp;s=c4b64e7c351dc417d537a40b33dc2d8f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F07b4c25986aa905337bfdaaf587a1f74&amp;w=552&amp;s=fe1c0c8cec3e3a7a1d4d397aa146e5be</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>b04b46bc38cc6bcb</t>
+          <t>9b30666639d331c7</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>1 flasker</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -3681,41 +3681,41 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fernet-Branca Bitter, Linie Aquavit eller Nordguld Akvavit</t>
+          <t>Roberto Sarotto Barbera d'Asti, Les Jablieres Côtes de Provence eller Cava Recoda</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fernet-Branca</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>70 cl</t>
+          <t>75 cl</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>200,00. kr/l</t>
+          <t>78,67. kr/l</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1029951</t>
+          <t>1029953</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F07b4c25986aa905337bfdaaf587a1f74&amp;w=552&amp;s=fe1c0c8cec3e3a7a1d4d397aa146e5be</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F45b1a86520da133df2472a02fb413c45&amp;w=1152&amp;s=b08d5ea2f2b7ab06394f82b48dce9fd3</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>9b30666639d331c7</t>
+          <t>9a6331c6cd396c9a</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3737,41 +3737,41 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Roberto Sarotto Barbera d'Asti, Les Jablieres Côtes de Provence eller Cava Recoda</t>
+          <t>Coop appelsin, multi- eller æblejuice</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Roberto</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>1 l</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>78,67. kr/l</t>
+          <t>15,00. kr/l</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1029953</t>
+          <t>1029955</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F45b1a86520da133df2472a02fb413c45&amp;w=1152&amp;s=b08d5ea2f2b7ab06394f82b48dce9fd3</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F58715c6f277033177224542ffd71fd14%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4681856bd6a3a5071e33737905504045%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fde00956562fcee2dc385672c8a4bb858&amp;w=552&amp;s=e8590833230c7a6306a0ab013261c982</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>9a6331c6cd396c9a</t>
+          <t>e87066c319364fbc</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -3793,41 +3793,41 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Coop appelsin, multi- eller æblejuice</t>
+          <t>Anarkist eller Willemoes øl</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Anarkist</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1 l</t>
+          <t>44-50 cl</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>15,00. kr/l</t>
+          <t>40,91 kr/l</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1029955</t>
+          <t>1029956</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F58715c6f277033177224542ffd71fd14%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4681856bd6a3a5071e33737905504045%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fde00956562fcee2dc385672c8a4bb858&amp;w=552&amp;s=e8590833230c7a6306a0ab013261c982</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F551ff59167ff38abad8b1495b38a276c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2a5b084f08ec9fc437b06379eaf95ecb%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F92aef8d00fc26cc29d2ed12524da5b2b&amp;w=552&amp;s=641aa0a8b6fb75d782e85d6cc7ea54f5</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>e87066c319364fbc</t>
+          <t>929292cd7a6bcd92</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 dåse/flaske</t>
         </is>
       </c>
     </row>
@@ -3849,22 +3849,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Anarkist eller Willemoes øl</t>
+          <t>Faxe Kondi, Pepsi Max eller Cocio</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Anarkist</t>
+          <t>Faxe</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>44-50 cl</t>
+          <t>60-150 cl</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>40,91 kr/l</t>
+          <t>30,00 kr/l</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -3873,17 +3873,17 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1029956</t>
+          <t>1029959</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F551ff59167ff38abad8b1495b38a276c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2a5b084f08ec9fc437b06379eaf95ecb%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F92aef8d00fc26cc29d2ed12524da5b2b&amp;w=552&amp;s=641aa0a8b6fb75d782e85d6cc7ea54f5</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fed53c072fdc149cc7d10fed548ee602b&amp;w=252&amp;s=6b83213f144ff56558ec2499e7544986</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>929292cd7a6bcd92</t>
+          <t>c0a4303f1f2f674b</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>1 dåse/flaske</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -3905,41 +3905,41 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Faxe Kondi, Pepsi Max eller Cocio</t>
+          <t>Carlsberg eller Tuborg</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Faxe</t>
+          <t>Carlsberg</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>60-150 cl</t>
+          <t>15-18 x 33 cl</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>30,00 kr/l</t>
+          <t>21,21 kr/l</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1029959</t>
+          <t>1029957</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fed53c072fdc149cc7d10fed548ee602b&amp;w=252&amp;s=6b83213f144ff56558ec2499e7544986</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1d8ff57f86b3ccb6e52029d8043a0fc4&amp;w=252&amp;s=35b88ef26dbb77f802b1020255e288bb</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>c0a4303f1f2f674b</t>
+          <t>95db6bc070e46a2e</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -3961,41 +3961,41 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Carlsberg eller Tuborg</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Carlsberg</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>15-18 x 33 cl</t>
+          <t>24 x 33 cl</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>21,21 kr/l</t>
+          <t>12,50 kr/l</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1029957</t>
+          <t>1029958</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1d8ff57f86b3ccb6e52029d8043a0fc4&amp;w=252&amp;s=35b88ef26dbb77f802b1020255e288bb</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc0ed255e6c3093b663c0b5fff55cf62c&amp;w=415&amp;s=e14240254977d009b64862d14e0ff1f0</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>95db6bc070e46a2e</t>
+          <t>c5624ac066bf38bd</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4017,41 +4017,41 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Xtra kyllingebryst eller -inderfilet</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Xtra</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>24 x 33 cl</t>
+          <t>600 g</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>12,50 kr/l</t>
+          <t>81,67. kr/kg</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1029958</t>
+          <t>1043648</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc0ed255e6c3093b663c0b5fff55cf62c&amp;w=415&amp;s=e14240254977d009b64862d14e0ff1f0</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9751d328ddbe09d3da2523b802dbadbb%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa86d0b8b5fd11fb3113e1eeb242fbf6b&amp;w=552&amp;s=5dce06b9ff3c91d7141ade977cfa84e5</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>c5624ac066bf38bd</t>
+          <t>d8ed1dce5a28661a</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4073,41 +4073,41 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Irma Vitendo tomater</t>
+          <t>Pågen brød</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Pågen</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>650-900 g</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>55,00. kr/kg</t>
+          <t>30,77. kr/kg</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1029918</t>
+          <t>1029925</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9214c0637e5db88b766d162f2be5cdba&amp;w=552&amp;s=99accb735acf04b56143b17b8901f70b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2f34c919c36beb31fbd04735bc4d1849%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fffb4ac0a867e103689274ee2eea247c9&amp;w=552&amp;s=82768826187e4288f009c2660607580c</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>cec6396b9230b399</t>
+          <t>d9e0661c770b3e34</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>1 bakke</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -4129,41 +4129,41 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bread &amp; Butter eller Terrunyo</t>
+          <t>Danske frilandsæg</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bread</t>
+          <t>Danske</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>10 stk</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>132,00. kr/l</t>
+          <t>2,60. kr/stk</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1029954</t>
+          <t>1029921</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5dd89b35680a0c14456e21ee6fde279c&amp;w=265&amp;s=b0cba3fb9ecd1c20b9c174139682bd65</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbe29c136be04a69154119eb4a7a28207&amp;w=252&amp;s=ef3ffad95a21f7dd15fea1b3931bfd09</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>dc2763a71ec8278a</t>
+          <t>ca6a3595eb4ac4a5</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 bakke</t>
         </is>
       </c>
     </row>
@@ -4185,41 +4185,41 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Dansk Kalv entrecote eller ribeye</t>
+          <t>Coop Kylling</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dansk</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>350 g</t>
+          <t>750-1500 g</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>282,86. kr/kg</t>
+          <t>50,67. kr/kg</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1029911</t>
+          <t>1029934</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8ffb5fbcc1ca0fe7443880ede1b148a3%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F502850b35cdec1e51ce717d700365acb&amp;w=252&amp;s=e6ece7abc7a477bdb0d4e862b3ab6a26</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F25f7d84484d16cb33ccea0ff03c6d5f0%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc1e84544869fd363dfae125fc838dccd%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8b289f68bfe8ed55c48973db006b5af9&amp;w=252&amp;s=6f8fd4efe81a6f7022809c64eb7c47ba</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>d07c07a2ccfc17c6</t>
+          <t>9d15dcea925ac439</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -4241,41 +4241,41 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sun Lolly</t>
+          <t>Pink Lady æbler</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Pink</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>8 x 60 ml</t>
+          <t>8 stk</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>33,33. kr/l</t>
+          <t>2,75. kr/stk</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1029944</t>
+          <t>1043649</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2d2ca6d7211333213152f539af36de40%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0e2162e38a5aff5c21383b1b1f0471ec%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5ec9e01846238e9e7460635c83b53d68&amp;w=252&amp;s=6a28ba2f432a7178ab4d67c3bcb5c5a0</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa58a25726c5bb867b1e32ab86c6316f6&amp;w=252&amp;s=2da8061ed049590b4d8db181aa96b57a</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>e2b117e6780f2559</t>
+          <t>c1943e4b4c7aeb8c</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 bakke</t>
         </is>
       </c>
     </row>
@@ -4297,41 +4297,41 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Valsemøllen kage-, brødblanding eller sukker</t>
+          <t>OTA solgryn</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Valsemøllen</t>
+          <t>OTA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>400-2000 g</t>
+          <t>700 g</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>42,50. kr/kg</t>
+          <t>17,14. kr/kg</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1029940</t>
+          <t>1029939</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F579b32a002ffa91cd94d35b2d784320d&amp;w=252&amp;s=a1d5f8f1eadd62b916f1e7d6ee52b8c6</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F82d642042711f4691600acd343a21fa0&amp;w=252&amp;s=33514fd82fe1636c03ee57a341bd6e9e</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>85c647f87c83236d</t>
+          <t>c3c3b69a6c689699</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4340,62 +4340,6 @@
         </is>
       </c>
       <c r="L70" t="inlineStr">
-        <is>
-          <t>1 pakke</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Langelænder pølser</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Langelænder</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>325-360 g</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>89,23. kr/kg</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>29</v>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>1029924</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb4c4e33e0c7e682696281fe491faceb9%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F063e68ae8d1b5b4ca16fe29584c62c9c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa190d6311262bd3cc9bd7e2b5e27e703&amp;w=252&amp;s=9de01174b01e6973f9abde5fd96ae4d6</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>83a55c58b1e7c639</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
         <is>
           <t>1 pakke</t>
         </is>
